--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/11.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/11.xlsx
@@ -426,13 +426,13 @@
         <v>-15.39047163574784</v>
       </c>
       <c r="E2">
-        <v>-5.488064255077316</v>
+        <v>-4.578737617389093</v>
       </c>
       <c r="F2">
-        <v>-5.20155763923761</v>
+        <v>-5.704105776596195</v>
       </c>
       <c r="G2">
-        <v>-9.778071492551723</v>
+        <v>-9.711205093749523</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-16.55103311052688</v>
       </c>
       <c r="E3">
-        <v>-6.308170897866417</v>
+        <v>-5.709633431324611</v>
       </c>
       <c r="F3">
-        <v>-5.109912868363692</v>
+        <v>-5.424728929593227</v>
       </c>
       <c r="G3">
-        <v>-9.265853955079066</v>
+        <v>-9.625852608656034</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-18.04243096083345</v>
       </c>
       <c r="E4">
-        <v>-8.070417501003321</v>
+        <v>-5.584729061245048</v>
       </c>
       <c r="F4">
-        <v>-5.366285952590917</v>
+        <v>-5.267068246920606</v>
       </c>
       <c r="G4">
-        <v>-9.157215092662343</v>
+        <v>-9.648122648498711</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-19.63212576382295</v>
       </c>
       <c r="E5">
-        <v>-7.712079352776366</v>
+        <v>-6.686624527635445</v>
       </c>
       <c r="F5">
-        <v>-5.128955378219247</v>
+        <v>-5.303985268593769</v>
       </c>
       <c r="G5">
-        <v>-8.867995902714995</v>
+        <v>-8.819661937841635</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-21.26399018111294</v>
       </c>
       <c r="E6">
-        <v>-8.323314660435681</v>
+        <v>-8.083581774943619</v>
       </c>
       <c r="F6">
-        <v>-5.444521940315719</v>
+        <v>-5.259221950881289</v>
       </c>
       <c r="G6">
-        <v>-8.493778456046858</v>
+        <v>-9.231765267661192</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-22.81046842788665</v>
       </c>
       <c r="E7">
-        <v>-8.737534177917288</v>
+        <v>-8.616913744248981</v>
       </c>
       <c r="F7">
-        <v>-5.13972084098603</v>
+        <v>-5.09565003842229</v>
       </c>
       <c r="G7">
-        <v>-7.51434362661686</v>
+        <v>-9.562061706659817</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-24.17310317270355</v>
       </c>
       <c r="E8">
-        <v>-9.587189113606438</v>
+        <v>-8.690261437751218</v>
       </c>
       <c r="F8">
-        <v>-5.16783728737185</v>
+        <v>-5.536225525275235</v>
       </c>
       <c r="G8">
-        <v>-8.260348579527308</v>
+        <v>-8.792694233878732</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-25.23406205615263</v>
       </c>
       <c r="E9">
-        <v>-10.1928408128143</v>
+        <v>-9.990064803698832</v>
       </c>
       <c r="F9">
-        <v>-4.888643509564902</v>
+        <v>-5.306214405274702</v>
       </c>
       <c r="G9">
-        <v>-7.75890355723944</v>
+        <v>-9.087435413785585</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-25.91228457304767</v>
       </c>
       <c r="E10">
-        <v>-10.89991221589794</v>
+        <v>-10.59575273069875</v>
       </c>
       <c r="F10">
-        <v>-4.771485851052162</v>
+        <v>-5.070705410821788</v>
       </c>
       <c r="G10">
-        <v>-7.450238222794413</v>
+        <v>-8.66887983070999</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-26.1436825344863</v>
       </c>
       <c r="E11">
-        <v>-12.28970994579999</v>
+        <v>-11.23324413065454</v>
       </c>
       <c r="F11">
-        <v>-4.871417609423687</v>
+        <v>-4.950480307816482</v>
       </c>
       <c r="G11">
-        <v>-8.104289462806063</v>
+        <v>-8.553815199401541</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-25.89646249531556</v>
       </c>
       <c r="E12">
-        <v>-12.13326928273101</v>
+        <v>-11.74215403963653</v>
       </c>
       <c r="F12">
-        <v>-4.171235092002988</v>
+        <v>-4.797109739922959</v>
       </c>
       <c r="G12">
-        <v>-6.328032806437805</v>
+        <v>-7.63167598161971</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-25.16349868225343</v>
       </c>
       <c r="E13">
-        <v>-12.37555169908939</v>
+        <v>-12.92298533645463</v>
       </c>
       <c r="F13">
-        <v>-4.451459358859018</v>
+        <v>-4.600679806064516</v>
       </c>
       <c r="G13">
-        <v>-6.564200504118332</v>
+        <v>-7.26537073879043</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-23.97832236196534</v>
       </c>
       <c r="E14">
-        <v>-13.6970826833258</v>
+        <v>-13.91000247421845</v>
       </c>
       <c r="F14">
-        <v>-4.525140982603229</v>
+        <v>-4.267673625036906</v>
       </c>
       <c r="G14">
-        <v>-5.913102270727712</v>
+        <v>-6.721021046313608</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-22.40253737402131</v>
       </c>
       <c r="E15">
-        <v>-14.32809836545062</v>
+        <v>-13.56227906906547</v>
       </c>
       <c r="F15">
-        <v>-4.029653848986107</v>
+        <v>-4.438663567587974</v>
       </c>
       <c r="G15">
-        <v>-5.864953696404551</v>
+        <v>-6.238118389591199</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-20.51816040490737</v>
       </c>
       <c r="E16">
-        <v>-15.2211632529773</v>
+        <v>-14.80709770361195</v>
       </c>
       <c r="F16">
-        <v>-3.681713032053425</v>
+        <v>-4.260904206621229</v>
       </c>
       <c r="G16">
-        <v>-4.351309375484518</v>
+        <v>-6.229643393010665</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-18.4171586523097</v>
       </c>
       <c r="E17">
-        <v>-15.00630980368338</v>
+        <v>-16.15351718099453</v>
       </c>
       <c r="F17">
-        <v>-3.62700599203774</v>
+        <v>-3.824821784561068</v>
       </c>
       <c r="G17">
-        <v>-4.600106804397366</v>
+        <v>-5.095073089064879</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-16.21255864571535</v>
       </c>
       <c r="E18">
-        <v>-16.41715588077308</v>
+        <v>-17.02235020410616</v>
       </c>
       <c r="F18">
-        <v>-3.414424550559512</v>
+        <v>-3.580330802359599</v>
       </c>
       <c r="G18">
-        <v>-4.438959379182262</v>
+        <v>-5.049983458820006</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-14.02407936214887</v>
       </c>
       <c r="E19">
-        <v>-16.91705865495382</v>
+        <v>-17.60764188417553</v>
       </c>
       <c r="F19">
-        <v>-2.970140462844233</v>
+        <v>-3.187504069338823</v>
       </c>
       <c r="G19">
-        <v>-3.935974953218634</v>
+        <v>-4.759406945201556</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-11.96635029806981</v>
       </c>
       <c r="E20">
-        <v>-18.75862148033507</v>
+        <v>-18.3735336361448</v>
       </c>
       <c r="F20">
-        <v>-2.718049209722079</v>
+        <v>-3.007155231870926</v>
       </c>
       <c r="G20">
-        <v>-3.471482240240111</v>
+        <v>-4.938285652324996</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-10.13759121838424</v>
       </c>
       <c r="E21">
-        <v>-18.25016441875384</v>
+        <v>-19.59241317157535</v>
       </c>
       <c r="F21">
-        <v>-2.589186719807782</v>
+        <v>-2.767820008384482</v>
       </c>
       <c r="G21">
-        <v>-4.244166879651545</v>
+        <v>-4.524292001002516</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-8.616859025158595</v>
       </c>
       <c r="E22">
-        <v>-19.26927032333601</v>
+        <v>-19.70051237461245</v>
       </c>
       <c r="F22">
-        <v>-2.390081159238296</v>
+        <v>-2.156233869795399</v>
       </c>
       <c r="G22">
-        <v>-3.878262212832519</v>
+        <v>-4.449288281264788</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-7.46286803680868</v>
       </c>
       <c r="E23">
-        <v>-20.14953774331701</v>
+        <v>-20.23329639856288</v>
       </c>
       <c r="F23">
-        <v>-2.728727693911567</v>
+        <v>-2.399159237605576</v>
       </c>
       <c r="G23">
-        <v>-3.77051388716586</v>
+        <v>-4.116346716380285</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-6.701250743139746</v>
       </c>
       <c r="E24">
-        <v>-20.40458592790301</v>
+        <v>-20.35340058619432</v>
       </c>
       <c r="F24">
-        <v>-2.015504188468596</v>
+        <v>-1.928056755224663</v>
       </c>
       <c r="G24">
-        <v>-4.469979190885233</v>
+        <v>-4.352742841703023</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-6.323601818111839</v>
       </c>
       <c r="E25">
-        <v>-20.3959003147563</v>
+        <v>-20.65328519193026</v>
       </c>
       <c r="F25">
-        <v>-1.876183560093956</v>
+        <v>-2.060699085597934</v>
       </c>
       <c r="G25">
-        <v>-4.421145333635444</v>
+        <v>-5.001987169591652</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-6.295536552823202</v>
       </c>
       <c r="E26">
-        <v>-21.17322646359494</v>
+        <v>-20.90254145826045</v>
       </c>
       <c r="F26">
-        <v>-1.770217145193037</v>
+        <v>-2.057474251298836</v>
       </c>
       <c r="G26">
-        <v>-4.205085889560449</v>
+        <v>-4.975165129632477</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-6.571616694746305</v>
       </c>
       <c r="E27">
-        <v>-21.49268313399204</v>
+        <v>-21.06792132902057</v>
       </c>
       <c r="F27">
-        <v>-1.772306287782898</v>
+        <v>-1.915540952135766</v>
       </c>
       <c r="G27">
-        <v>-5.785219207091204</v>
+        <v>-4.844540934289454</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-7.093017007936312</v>
       </c>
       <c r="E28">
-        <v>-21.0842872340843</v>
+        <v>-21.20117167669628</v>
       </c>
       <c r="F28">
-        <v>-1.702760702480865</v>
+        <v>-2.079360546448202</v>
       </c>
       <c r="G28">
-        <v>-5.912476577620789</v>
+        <v>-5.189655375121857</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-7.792521952545933</v>
       </c>
       <c r="E29">
-        <v>-21.27614056389326</v>
+        <v>-20.6317568264978</v>
       </c>
       <c r="F29">
-        <v>-1.835322681216064</v>
+        <v>-2.099840273747614</v>
       </c>
       <c r="G29">
-        <v>-4.594339834067955</v>
+        <v>-5.484476008121653</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-8.602042140526427</v>
       </c>
       <c r="E30">
-        <v>-20.72165156402406</v>
+        <v>-20.54825629427036</v>
       </c>
       <c r="F30">
-        <v>-2.029000778562408</v>
+        <v>-2.01844075091152</v>
       </c>
       <c r="G30">
-        <v>-5.437267628731646</v>
+        <v>-5.468297372071235</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-9.465709229728564</v>
       </c>
       <c r="E31">
-        <v>-19.75254454096058</v>
+        <v>-20.9526943078954</v>
       </c>
       <c r="F31">
-        <v>-1.76554266793904</v>
+        <v>-2.021579435000727</v>
       </c>
       <c r="G31">
-        <v>-5.291904884647787</v>
+        <v>-5.337113694532074</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-10.34023395869763</v>
       </c>
       <c r="E32">
-        <v>-20.784787548639</v>
+        <v>-20.57782722954045</v>
       </c>
       <c r="F32">
-        <v>-2.02882682140782</v>
+        <v>-2.262578848599396</v>
       </c>
       <c r="G32">
-        <v>-4.728171948038533</v>
+        <v>-5.25237034981781</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-11.1879639354396</v>
       </c>
       <c r="E33">
-        <v>-19.5248438109069</v>
+        <v>-20.27579612712487</v>
       </c>
       <c r="F33">
-        <v>-2.023347171038302</v>
+        <v>-2.106816784013991</v>
       </c>
       <c r="G33">
-        <v>-5.4470171853448</v>
+        <v>-5.310013568747601</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-11.9791908486787</v>
       </c>
       <c r="E34">
-        <v>-18.71289294980561</v>
+        <v>-19.45738766208864</v>
       </c>
       <c r="F34">
-        <v>-2.284560406000084</v>
+        <v>-1.952298927267591</v>
       </c>
       <c r="G34">
-        <v>-5.403807944966232</v>
+        <v>-4.869681217114679</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-12.69480593418127</v>
       </c>
       <c r="E35">
-        <v>-19.06957367654576</v>
+        <v>-19.19574601934747</v>
       </c>
       <c r="F35">
-        <v>-1.646619758490934</v>
+        <v>-2.080381923455853</v>
       </c>
       <c r="G35">
-        <v>-5.4476494995428</v>
+        <v>-5.780733417885492</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-13.3322647745281</v>
       </c>
       <c r="E36">
-        <v>-18.87042497511044</v>
+        <v>-18.04624723418845</v>
       </c>
       <c r="F36">
-        <v>-1.594933774393259</v>
+        <v>-2.074987594928823</v>
       </c>
       <c r="G36">
-        <v>-5.431626459132728</v>
+        <v>-5.507252561431838</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-13.89145488590204</v>
       </c>
       <c r="E37">
-        <v>-18.68010679799008</v>
+        <v>-17.96000244671236</v>
       </c>
       <c r="F37">
-        <v>-2.29942214557371</v>
+        <v>-1.93660136498454</v>
       </c>
       <c r="G37">
-        <v>-5.557264972893608</v>
+        <v>-5.105411922784024</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-14.37209898856979</v>
       </c>
       <c r="E38">
-        <v>-17.33000114276526</v>
+        <v>-17.79934577434224</v>
       </c>
       <c r="F38">
-        <v>-1.536863562722208</v>
+        <v>-1.925665258532781</v>
       </c>
       <c r="G38">
-        <v>-5.032679237286235</v>
+        <v>-4.678632944588879</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-14.77264747427574</v>
       </c>
       <c r="E39">
-        <v>-17.58934232071054</v>
+        <v>-17.78600036144164</v>
       </c>
       <c r="F39">
-        <v>-1.592525710353321</v>
+        <v>-2.252906830804309</v>
       </c>
       <c r="G39">
-        <v>-5.669373287035488</v>
+        <v>-4.175804114265596</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-15.09398613241053</v>
       </c>
       <c r="E40">
-        <v>-16.8298493025141</v>
+        <v>-16.93327964884929</v>
       </c>
       <c r="F40">
-        <v>-1.9222383025874</v>
+        <v>-2.146350618312598</v>
       </c>
       <c r="G40">
-        <v>-4.915068796458087</v>
+        <v>-4.109179385287763</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-15.33125488908912</v>
       </c>
       <c r="E41">
-        <v>-16.40426784374725</v>
+        <v>-17.11284722867545</v>
       </c>
       <c r="F41">
-        <v>-1.464954645219989</v>
+        <v>-2.040111670536158</v>
       </c>
       <c r="G41">
-        <v>-4.157241885426902</v>
+        <v>-4.060848730959942</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-15.47385593397741</v>
       </c>
       <c r="E42">
-        <v>-14.66817317800464</v>
+        <v>-16.47063263032966</v>
       </c>
       <c r="F42">
-        <v>-2.079508824213303</v>
+        <v>-2.225641946108566</v>
       </c>
       <c r="G42">
-        <v>-4.31759477971258</v>
+        <v>-4.150733352896695</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-15.5102351989707</v>
       </c>
       <c r="E43">
-        <v>-14.2712297888623</v>
+        <v>-15.68155961991512</v>
       </c>
       <c r="F43">
-        <v>-2.095399396101206</v>
+        <v>-1.979121463770239</v>
       </c>
       <c r="G43">
-        <v>-4.43247402047083</v>
+        <v>-4.095056598017232</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-15.43619103568611</v>
       </c>
       <c r="E44">
-        <v>-15.53936100760026</v>
+        <v>-14.54611268960189</v>
       </c>
       <c r="F44">
-        <v>-2.016606745481722</v>
+        <v>-2.213763985919824</v>
       </c>
       <c r="G44">
-        <v>-4.282599002816944</v>
+        <v>-4.149683909960745</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-15.25227753844767</v>
       </c>
       <c r="E45">
-        <v>-14.14801001111359</v>
+        <v>-13.58088204028898</v>
       </c>
       <c r="F45">
-        <v>-2.358763901208058</v>
+        <v>-2.225855664898488</v>
       </c>
       <c r="G45">
-        <v>-4.406423337622305</v>
+        <v>-4.207919716542065</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-14.9634685903991</v>
       </c>
       <c r="E46">
-        <v>-14.26803268621288</v>
+        <v>-13.76734648602882</v>
       </c>
       <c r="F46">
-        <v>-2.446357127114883</v>
+        <v>-2.222462672016622</v>
       </c>
       <c r="G46">
-        <v>-4.323590177684201</v>
+        <v>-4.067274499851668</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-14.58052157001759</v>
       </c>
       <c r="E47">
-        <v>-14.03353471667369</v>
+        <v>-13.62921897184685</v>
       </c>
       <c r="F47">
-        <v>-2.376372507089367</v>
+        <v>-2.375127470882959</v>
       </c>
       <c r="G47">
-        <v>-4.775370395791922</v>
+        <v>-4.438005942066952</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-14.12577533636497</v>
       </c>
       <c r="E48">
-        <v>-12.45406185296037</v>
+        <v>-12.52870016155479</v>
       </c>
       <c r="F48">
-        <v>-2.337095466685629</v>
+        <v>-2.630595977906327</v>
       </c>
       <c r="G48">
-        <v>-4.396074572266543</v>
+        <v>-3.621496300806646</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-13.6278413536828</v>
       </c>
       <c r="E49">
-        <v>-11.52765381131521</v>
+        <v>-12.96265929723583</v>
       </c>
       <c r="F49">
-        <v>-2.297561632387022</v>
+        <v>-2.614175250880632</v>
       </c>
       <c r="G49">
-        <v>-4.144873687292185</v>
+        <v>-4.379260311472585</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-13.11612403217221</v>
       </c>
       <c r="E50">
-        <v>-11.65098680091411</v>
+        <v>-11.55431746627237</v>
       </c>
       <c r="F50">
-        <v>-2.606154997686728</v>
+        <v>-2.634648351240822</v>
       </c>
       <c r="G50">
-        <v>-4.434894029260037</v>
+        <v>-3.471038627137849</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-12.61866631352282</v>
       </c>
       <c r="E51">
-        <v>-11.42366193420307</v>
+        <v>-12.18249379519438</v>
       </c>
       <c r="F51">
-        <v>-2.825797442906419</v>
+        <v>-2.950615843160249</v>
       </c>
       <c r="G51">
-        <v>-3.725576542015792</v>
+        <v>-3.883396868963929</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-12.17084061101626</v>
       </c>
       <c r="E52">
-        <v>-10.53667425879468</v>
+        <v>-11.02863861803998</v>
       </c>
       <c r="F52">
-        <v>-2.707505749419247</v>
+        <v>-2.642831792813078</v>
       </c>
       <c r="G52">
-        <v>-3.939454336580408</v>
+        <v>-3.735279750991396</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-11.81013122502817</v>
       </c>
       <c r="E53">
-        <v>-11.51511446678797</v>
+        <v>-10.4266957390444</v>
       </c>
       <c r="F53">
-        <v>-2.922384253705439</v>
+        <v>-2.715826699980368</v>
       </c>
       <c r="G53">
-        <v>-4.050807846339334</v>
+        <v>-3.941854482096379</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-11.56485042166368</v>
       </c>
       <c r="E54">
-        <v>-11.35789943466368</v>
+        <v>-10.63017819010506</v>
       </c>
       <c r="F54">
-        <v>-2.530462926255923</v>
+        <v>-2.905505439505996</v>
       </c>
       <c r="G54">
-        <v>-3.802497067620759</v>
+        <v>-4.04178329919928</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-11.44884580614094</v>
       </c>
       <c r="E55">
-        <v>-9.017996158634336</v>
+        <v>-9.980523308964671</v>
       </c>
       <c r="F55">
-        <v>-2.962794500716207</v>
+        <v>-2.734256217957852</v>
       </c>
       <c r="G55">
-        <v>-5.133809782419892</v>
+        <v>-4.345601994974815</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-11.46918931562681</v>
       </c>
       <c r="E56">
-        <v>-9.485384489440001</v>
+        <v>-9.699490740522656</v>
       </c>
       <c r="F56">
-        <v>-2.687521385826709</v>
+        <v>-3.006918318793725</v>
       </c>
       <c r="G56">
-        <v>-5.009843094156342</v>
+        <v>-4.225545060993145</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-11.62805887459913</v>
       </c>
       <c r="E57">
-        <v>-8.889627505938904</v>
+        <v>-8.829149735566467</v>
       </c>
       <c r="F57">
-        <v>-2.962903845213376</v>
+        <v>-3.025110923694008</v>
       </c>
       <c r="G57">
-        <v>-4.848424204207019</v>
+        <v>-3.975933237877637</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-11.91392786503386</v>
       </c>
       <c r="E58">
-        <v>-8.52551555335217</v>
+        <v>-8.927847826563642</v>
       </c>
       <c r="F58">
-        <v>-2.661325095080577</v>
+        <v>-2.967643763492195</v>
       </c>
       <c r="G58">
-        <v>-5.499254283408959</v>
+        <v>-4.105782765564471</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-12.30295803556586</v>
       </c>
       <c r="E59">
-        <v>-7.816342938328969</v>
+        <v>-7.716884063698505</v>
       </c>
       <c r="F59">
-        <v>-2.628872973708504</v>
+        <v>-2.852429454906424</v>
       </c>
       <c r="G59">
-        <v>-5.126364365502071</v>
+        <v>-4.069469391544205</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-12.76791426761425</v>
       </c>
       <c r="E60">
-        <v>-7.768771318878391</v>
+        <v>-8.209926199757623</v>
       </c>
       <c r="F60">
-        <v>-3.02120848485942</v>
+        <v>-2.876356018968884</v>
       </c>
       <c r="G60">
-        <v>-4.435278052542593</v>
+        <v>-4.167792594060559</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-13.28538787289853</v>
       </c>
       <c r="E61">
-        <v>-7.145114407016037</v>
+        <v>-7.954791974165475</v>
       </c>
       <c r="F61">
-        <v>-2.90646220385623</v>
+        <v>-3.005756119327598</v>
       </c>
       <c r="G61">
-        <v>-5.121223088279582</v>
+        <v>-5.03070284159929</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-13.82939706566685</v>
       </c>
       <c r="E62">
-        <v>-7.072550139517128</v>
+        <v>-7.430661864043699</v>
       </c>
       <c r="F62">
-        <v>-2.91487758830127</v>
+        <v>-3.109731138992186</v>
       </c>
       <c r="G62">
-        <v>-4.66486107514551</v>
+        <v>-4.678613081315643</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-14.37100577953511</v>
       </c>
       <c r="E63">
-        <v>-8.224639211808544</v>
+        <v>-8.193474253687755</v>
       </c>
       <c r="F63">
-        <v>-2.92819607940348</v>
+        <v>-3.03268054502079</v>
       </c>
       <c r="G63">
-        <v>-6.479506817587158</v>
+        <v>-4.99064193002857</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-14.88290551954976</v>
       </c>
       <c r="E64">
-        <v>-7.391875484168003</v>
+        <v>-7.350190880927397</v>
       </c>
       <c r="F64">
-        <v>-3.038624909503279</v>
+        <v>-3.179335538379818</v>
       </c>
       <c r="G64">
-        <v>-5.844865306072253</v>
+        <v>-4.742582752770979</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-15.34638243934069</v>
       </c>
       <c r="E65">
-        <v>-6.759786553703367</v>
+        <v>-6.815264888771337</v>
       </c>
       <c r="F65">
-        <v>-3.017063334375811</v>
+        <v>-3.086698383357346</v>
       </c>
       <c r="G65">
-        <v>-5.57269873619769</v>
+        <v>-5.218228693671307</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-15.7460123529782</v>
       </c>
       <c r="E66">
-        <v>-6.650985437195079</v>
+        <v>-7.173073205539395</v>
       </c>
       <c r="F66">
-        <v>-3.108416519923944</v>
+        <v>-3.263621921614667</v>
       </c>
       <c r="G66">
-        <v>-6.150683571353508</v>
+        <v>-5.022608557755772</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-16.06773028885506</v>
       </c>
       <c r="E67">
-        <v>-5.515982297334603</v>
+        <v>-6.583560987694875</v>
       </c>
       <c r="F67">
-        <v>-3.283357774986365</v>
+        <v>-3.031515860452454</v>
       </c>
       <c r="G67">
-        <v>-6.325715424560315</v>
+        <v>-5.245080528540336</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-16.30162678595913</v>
       </c>
       <c r="E68">
-        <v>-6.678427989681562</v>
+        <v>-7.069679086996265</v>
       </c>
       <c r="F68">
-        <v>-3.332352393392345</v>
+        <v>-2.898942284573616</v>
       </c>
       <c r="G68">
-        <v>-5.657687061281861</v>
+        <v>-5.744297553680274</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-16.45006460479001</v>
       </c>
       <c r="E69">
-        <v>-5.414308998914389</v>
+        <v>-5.937175664788024</v>
       </c>
       <c r="F69">
-        <v>-3.332530492383947</v>
+        <v>-3.331543906807213</v>
       </c>
       <c r="G69">
-        <v>-5.53799759785505</v>
+        <v>-5.151868808336616</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-16.5263188595609</v>
       </c>
       <c r="E70">
-        <v>-6.54317605649447</v>
+        <v>-5.863945711609986</v>
       </c>
       <c r="F70">
-        <v>-3.308223707683601</v>
+        <v>-3.117865706887677</v>
       </c>
       <c r="G70">
-        <v>-5.210849487664271</v>
+        <v>-5.745171537702641</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-16.54542745679009</v>
       </c>
       <c r="E71">
-        <v>-7.009713034186694</v>
+        <v>-6.308913567603676</v>
       </c>
       <c r="F71">
-        <v>-3.767114397812443</v>
+        <v>-3.523200787690726</v>
       </c>
       <c r="G71">
-        <v>-5.12105093991154</v>
+        <v>-4.96470380572838</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-16.52252789997106</v>
       </c>
       <c r="E72">
-        <v>-6.60448706608432</v>
+        <v>-6.217832369887401</v>
       </c>
       <c r="F72">
-        <v>-3.542881140446437</v>
+        <v>-3.349437471075085</v>
       </c>
       <c r="G72">
-        <v>-5.143320979754217</v>
+        <v>-4.753126840313558</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-16.47868938196802</v>
       </c>
       <c r="E73">
-        <v>-6.19485942124649</v>
+        <v>-6.436838429846356</v>
       </c>
       <c r="F73">
-        <v>-3.443277415566421</v>
+        <v>-3.233124747313201</v>
       </c>
       <c r="G73">
-        <v>-5.533852794839882</v>
+        <v>-5.039412886913113</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-16.44053351277662</v>
       </c>
       <c r="E74">
-        <v>-5.918830816582951</v>
+        <v>-6.384398700837533</v>
       </c>
       <c r="F74">
-        <v>-3.571409285431449</v>
+        <v>-3.215528566942933</v>
       </c>
       <c r="G74">
-        <v>-4.805072610370263</v>
+        <v>-4.249102903050598</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-16.42513704618073</v>
       </c>
       <c r="E75">
-        <v>-5.92087315836041</v>
+        <v>-7.343108347579401</v>
       </c>
       <c r="F75">
-        <v>-3.598615356041593</v>
+        <v>-3.540917081334399</v>
       </c>
       <c r="G75">
-        <v>-4.55911562953011</v>
+        <v>-4.670396307287172</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-16.43916721414407</v>
       </c>
       <c r="E76">
-        <v>-6.9356226709472</v>
+        <v>-6.848272935813246</v>
       </c>
       <c r="F76">
-        <v>-3.881780327177562</v>
+        <v>-3.64312353659401</v>
       </c>
       <c r="G76">
-        <v>-4.357536511643887</v>
+        <v>-4.146058862595244</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-16.48692386801325</v>
       </c>
       <c r="E77">
-        <v>-8.385395510606834</v>
+        <v>-7.061627460210627</v>
       </c>
       <c r="F77">
-        <v>-3.430470855519141</v>
+        <v>-3.474560710533145</v>
       </c>
       <c r="G77">
-        <v>-4.946144887435226</v>
+        <v>-4.114224656689612</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-16.57480973264178</v>
       </c>
       <c r="E78">
-        <v>-7.097665056363668</v>
+        <v>-7.73895584601189</v>
       </c>
       <c r="F78">
-        <v>-3.880768062211341</v>
+        <v>-3.832086566683619</v>
       </c>
       <c r="G78">
-        <v>-4.990009615830569</v>
+        <v>-3.705630505141684</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-16.70117879137677</v>
       </c>
       <c r="E79">
-        <v>-8.276014749425563</v>
+        <v>-8.590567082472354</v>
       </c>
       <c r="F79">
-        <v>-4.120045299979589</v>
+        <v>-4.092101982380954</v>
       </c>
       <c r="G79">
-        <v>-4.700681177880424</v>
+        <v>-3.865178936861319</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-16.85611679149497</v>
       </c>
       <c r="E80">
-        <v>-9.629104669021435</v>
+        <v>-8.892435159823661</v>
       </c>
       <c r="F80">
-        <v>-4.149965930568707</v>
+        <v>-3.82995931919323</v>
       </c>
       <c r="G80">
-        <v>-3.34752548361318</v>
+        <v>-3.340901081989098</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-17.0275201580538</v>
       </c>
       <c r="E81">
-        <v>-9.87691635214318</v>
+        <v>-9.134355298261426</v>
       </c>
       <c r="F81">
-        <v>-3.944032965865348</v>
+        <v>-4.10063168152758</v>
       </c>
       <c r="G81">
-        <v>-4.402126249512331</v>
+        <v>-3.169348612144065</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-17.20844443123909</v>
       </c>
       <c r="E82">
-        <v>-10.97440108485011</v>
+        <v>-10.28567452997154</v>
       </c>
       <c r="F82">
-        <v>-4.194048330276086</v>
+        <v>-3.775181867948307</v>
       </c>
       <c r="G82">
-        <v>-3.438058972475629</v>
+        <v>-3.215418163868563</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-17.38897547373371</v>
       </c>
       <c r="E83">
-        <v>-12.11293190596256</v>
+        <v>-11.06125721631722</v>
       </c>
       <c r="F83">
-        <v>-4.156291344056484</v>
+        <v>-4.385058256218013</v>
       </c>
       <c r="G83">
-        <v>-3.160678293376714</v>
+        <v>-2.940540257197338</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-17.5551014345278</v>
       </c>
       <c r="E84">
-        <v>-11.36051236416611</v>
+        <v>-11.53019428523351</v>
       </c>
       <c r="F84">
-        <v>-4.200469834382588</v>
+        <v>-4.300311300707206</v>
       </c>
       <c r="G84">
-        <v>-3.332555196684596</v>
+        <v>-2.774625646405684</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-17.69292645602741</v>
       </c>
       <c r="E85">
-        <v>-12.88989124840658</v>
+        <v>-12.44454300059624</v>
       </c>
       <c r="F85">
-        <v>-4.67545735988263</v>
+        <v>-4.838615088640228</v>
       </c>
       <c r="G85">
-        <v>-4.014040927580187</v>
+        <v>-2.69092512353629</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-17.79626463353964</v>
       </c>
       <c r="E86">
-        <v>-14.54986226608025</v>
+        <v>-13.35982458160455</v>
       </c>
       <c r="F86">
-        <v>-5.017148973128593</v>
+        <v>-4.641167919611147</v>
       </c>
       <c r="G86">
-        <v>-3.465966871371685</v>
+        <v>-2.468969597855853</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-17.86095739961788</v>
       </c>
       <c r="E87">
-        <v>-16.41287194436182</v>
+        <v>-15.21783935305567</v>
       </c>
       <c r="F87">
-        <v>-4.63432146302701</v>
+        <v>-4.692279845098682</v>
       </c>
       <c r="G87">
-        <v>-4.311073005000217</v>
+        <v>-2.967114006241067</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-17.88158400340342</v>
       </c>
       <c r="E88">
-        <v>-16.48726571535983</v>
+        <v>-15.70113168457627</v>
       </c>
       <c r="F88">
-        <v>-4.677655846969659</v>
+        <v>-4.82184976077497</v>
       </c>
       <c r="G88">
-        <v>-3.861825354230037</v>
+        <v>-2.016619965915377</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-17.8543499126457</v>
       </c>
       <c r="E89">
-        <v>-18.55266195399221</v>
+        <v>-17.6230341673276</v>
       </c>
       <c r="F89">
-        <v>-5.112174311373335</v>
+        <v>-5.169735077091664</v>
       </c>
       <c r="G89">
-        <v>-3.520587562224121</v>
+        <v>-2.039843442873365</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-17.78672892348212</v>
       </c>
       <c r="E90">
-        <v>-20.29527762230586</v>
+        <v>-19.56123009955853</v>
       </c>
       <c r="F90">
-        <v>-5.004574355954095</v>
+        <v>-5.342495240782515</v>
       </c>
       <c r="G90">
-        <v>-3.711755014389335</v>
+        <v>-2.308586908660321</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-17.69494055158825</v>
       </c>
       <c r="E91">
-        <v>-22.18318485068162</v>
+        <v>-20.28616180412843</v>
       </c>
       <c r="F91">
-        <v>-4.974980930489084</v>
+        <v>-5.240857873928626</v>
       </c>
       <c r="G91">
-        <v>-2.984878393604796</v>
+        <v>-2.617212516558878</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-17.59452923639691</v>
       </c>
       <c r="E92">
-        <v>-23.57664158758186</v>
+        <v>-23.2179456899083</v>
       </c>
       <c r="F92">
-        <v>-5.595201970884949</v>
+        <v>-5.338857879516822</v>
       </c>
       <c r="G92">
-        <v>-3.860673284382371</v>
+        <v>-2.900982548548586</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-17.49854302331078</v>
       </c>
       <c r="E93">
-        <v>-25.89004876219233</v>
+        <v>-25.00777069975192</v>
       </c>
       <c r="F93">
-        <v>-5.40177983906607</v>
+        <v>-5.880286269293205</v>
       </c>
       <c r="G93">
-        <v>-4.094404420545995</v>
+        <v>-3.144251366410851</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-17.42607771347909</v>
       </c>
       <c r="E94">
-        <v>-28.19253325749629</v>
+        <v>-27.3267977106059</v>
       </c>
       <c r="F94">
-        <v>-6.027404320030397</v>
+        <v>-5.587797194671324</v>
       </c>
       <c r="G94">
-        <v>-4.208002480180547</v>
+        <v>-3.130803930430331</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-17.39962343687583</v>
       </c>
       <c r="E95">
-        <v>-30.05786151446979</v>
+        <v>-29.2535818883375</v>
       </c>
       <c r="F95">
-        <v>-4.944019870442049</v>
+        <v>-5.579707358615584</v>
       </c>
       <c r="G95">
-        <v>-4.313036158505004</v>
+        <v>-3.434960301850872</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-17.4315333415954</v>
       </c>
       <c r="E96">
-        <v>-33.27627742680217</v>
+        <v>-31.68826612534738</v>
       </c>
       <c r="F96">
-        <v>-5.706665431870845</v>
+        <v>-5.925454658665653</v>
       </c>
       <c r="G96">
-        <v>-4.973463509225292</v>
+        <v>-3.84160123153063</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-17.51706671462587</v>
       </c>
       <c r="E97">
-        <v>-35.03120375170567</v>
+        <v>-34.28194055629256</v>
       </c>
       <c r="F97">
-        <v>-5.497854718810159</v>
+        <v>-6.271217697696375</v>
       </c>
       <c r="G97">
-        <v>-5.171775118664254</v>
+        <v>-4.022012721238752</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-17.65535732906294</v>
       </c>
       <c r="E98">
-        <v>-38.22463833717473</v>
+        <v>-37.43873752280256</v>
       </c>
       <c r="F98">
-        <v>-5.575505050781183</v>
+        <v>-5.883273362147699</v>
       </c>
       <c r="G98">
-        <v>-6.466810875444053</v>
+        <v>-4.590476427423626</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-17.83497398429005</v>
       </c>
       <c r="E99">
-        <v>-40.76859012351569</v>
+        <v>-39.04316001406114</v>
       </c>
       <c r="F99">
-        <v>-6.746565563016635</v>
+        <v>-6.331287588277783</v>
       </c>
       <c r="G99">
-        <v>-5.816838227536784</v>
+        <v>-5.347869656989166</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-18.05772685734415</v>
       </c>
       <c r="E100">
-        <v>-42.47954496580471</v>
+        <v>-41.5019176188958</v>
       </c>
       <c r="F100">
-        <v>-6.154719419636264</v>
+        <v>-6.327086108810785</v>
       </c>
       <c r="G100">
-        <v>-6.127423678394589</v>
+        <v>-5.400305387785683</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-18.28814820582055</v>
       </c>
       <c r="E101">
-        <v>-45.53145341734906</v>
+        <v>-43.72345564131266</v>
       </c>
       <c r="F101">
-        <v>-5.9690541201772</v>
+        <v>-6.520465165524718</v>
       </c>
       <c r="G101">
-        <v>-6.002894197389364</v>
+        <v>-5.239743929131031</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-18.54407971603761</v>
       </c>
       <c r="E102">
-        <v>-47.72684629508263</v>
+        <v>-46.61886003115191</v>
       </c>
       <c r="F102">
-        <v>-6.230513380257613</v>
+        <v>-6.422112689606632</v>
       </c>
       <c r="G102">
-        <v>-7.536315717361003</v>
+        <v>-6.164369366612855</v>
       </c>
     </row>
   </sheetData>
